--- a/data/trans_orig/P79A2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>37094</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>42156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>29649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>57642</t>
+          <t>77906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45777</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66828</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23076</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>102720</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>102720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>102720</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>39613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65387</t>
+          <t>90492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>116904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
